--- a/vendedores.xlsx
+++ b/vendedores.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>NOME</t>
   </si>
@@ -34,6 +34,12 @@
   </si>
   <si>
     <t>(47) 99911-0041</t>
+  </si>
+  <si>
+    <t>TESTE</t>
+  </si>
+  <si>
+    <t>(XX) 99999-9999</t>
   </si>
 </sst>
 </file>
@@ -372,7 +378,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
@@ -403,6 +409,14 @@
         <v>5</v>
       </c>
     </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/vendedores.xlsx
+++ b/vendedores.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>NOME</t>
   </si>
@@ -29,25 +29,21 @@
   <si>
     <t>(11) 91371-3031</t>
   </si>
-  <si>
-    <t>BRUNO A</t>
-  </si>
-  <si>
-    <t>(47) 99911-0041</t>
-  </si>
-  <si>
-    <t>TESTE</t>
-  </si>
-  <si>
-    <t>(XX) 99999-9999</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -75,8 +71,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -378,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
@@ -386,10 +383,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -401,24 +398,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
